--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="95">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
   </si>
   <si>
     <t xml:space="preserve">10</t>
@@ -372,7 +375,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -380,7 +383,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -388,7 +391,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -396,7 +399,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -404,7 +407,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -412,7 +415,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -420,7 +423,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -428,7 +431,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -436,7 +439,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -460,7 +463,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -484,7 +487,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -492,7 +495,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -508,7 +511,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -516,7 +519,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -524,7 +527,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -532,7 +535,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
@@ -540,7 +543,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -548,7 +551,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
@@ -556,7 +559,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
@@ -612,7 +615,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
@@ -620,7 +623,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -636,7 +639,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
@@ -644,7 +647,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -652,7 +655,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -660,7 +663,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
@@ -676,7 +679,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
@@ -684,7 +687,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -692,7 +695,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
@@ -700,7 +703,7 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
@@ -716,7 +719,7 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -724,7 +727,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48">
@@ -732,7 +735,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
@@ -740,7 +743,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50">
@@ -748,7 +751,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51">
@@ -756,7 +759,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52">
@@ -764,7 +767,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
@@ -772,7 +775,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54">
@@ -780,7 +783,7 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55">
@@ -796,7 +799,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57">
@@ -804,7 +807,7 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58">
@@ -812,7 +815,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59">
@@ -836,7 +839,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62">
@@ -844,7 +847,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
@@ -852,7 +855,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64">
@@ -868,7 +871,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66">
@@ -901,6 +904,14 @@
       </c>
       <c r="B69" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="98">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,211 +26,220 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 20.7</t>
@@ -375,7 +384,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -383,7 +392,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -391,7 +400,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -399,7 +408,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -407,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -415,7 +424,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -423,7 +432,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -431,7 +440,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -439,7 +448,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -447,7 +456,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -455,7 +464,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
@@ -463,7 +472,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -471,7 +480,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -479,7 +488,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -487,7 +496,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -495,7 +504,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
@@ -503,7 +512,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -519,7 +528,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
@@ -527,7 +536,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
@@ -535,7 +544,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -543,7 +552,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -551,7 +560,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -559,7 +568,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -567,7 +576,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -575,7 +584,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29">
@@ -583,7 +592,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
@@ -591,7 +600,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
@@ -599,7 +608,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
@@ -607,7 +616,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
@@ -615,7 +624,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
@@ -623,7 +632,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
@@ -631,7 +640,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
@@ -639,7 +648,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
@@ -647,7 +656,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38">
@@ -655,7 +664,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
@@ -663,7 +672,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
@@ -671,7 +680,7 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
@@ -679,7 +688,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
@@ -687,7 +696,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
@@ -695,7 +704,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44">
@@ -703,7 +712,7 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
@@ -711,7 +720,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
@@ -719,7 +728,7 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -727,7 +736,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48">
@@ -735,7 +744,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -743,7 +752,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
@@ -751,7 +760,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
@@ -759,7 +768,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52">
@@ -767,7 +776,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53">
@@ -775,7 +784,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
@@ -783,7 +792,7 @@
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55">
@@ -791,7 +800,7 @@
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56">
@@ -799,7 +808,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57">
@@ -807,7 +816,7 @@
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58">
@@ -815,7 +824,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59">
@@ -823,7 +832,7 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60">
@@ -831,7 +840,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61">
@@ -839,7 +848,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62">
@@ -847,7 +856,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63">
@@ -855,7 +864,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64">
@@ -863,7 +872,7 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65">
@@ -871,7 +880,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66">
@@ -879,7 +888,7 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67">
@@ -887,7 +896,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68">
@@ -895,7 +904,7 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69">
@@ -903,7 +912,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70">
@@ -911,7 +920,23 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
